--- a/hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx
+++ b/hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx
@@ -6835,26 +6835,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6873,7 +6854,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D37:F37</t>
+      <t xml:space="preserve">SIF_hbm_den_25</t>
     </r>
   </si>
   <si>
@@ -6997,26 +6978,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7035,7 +6997,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D38:F38</t>
+      <t xml:space="preserve">SIF_hbm_den_26</t>
     </r>
   </si>
   <si>
@@ -7081,26 +7043,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7119,7 +7062,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D39:F39</t>
+      <t xml:space="preserve">SIF_hbm_den_27</t>
     </r>
   </si>
   <si>
@@ -7165,26 +7108,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7203,7 +7127,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D40:F40</t>
+      <t xml:space="preserve">SIF_hbm_den_28</t>
     </r>
   </si>
   <si>
@@ -7249,26 +7173,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7287,7 +7192,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D41:F41</t>
+      <t xml:space="preserve">SIF_hbm_den_29</t>
     </r>
   </si>
   <si>
@@ -7333,26 +7238,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7371,7 +7257,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D42:F42</t>
+      <t xml:space="preserve">SIF_hbm_den_30</t>
     </r>
   </si>
   <si>
@@ -7420,26 +7306,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7458,7 +7325,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D43:F43</t>
+      <t xml:space="preserve">SIF_hbm_stk_25</t>
     </r>
   </si>
   <si>
@@ -7534,26 +7401,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7572,7 +7420,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D44:F44</t>
+      <t xml:space="preserve">SIF_hbm_stk_26</t>
     </r>
   </si>
   <si>
@@ -7618,26 +7466,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7656,7 +7485,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D45:F45</t>
+      <t xml:space="preserve">SIF_hbm_stk_27</t>
     </r>
   </si>
   <si>
@@ -7702,26 +7531,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7740,7 +7550,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D46:F46</t>
+      <t xml:space="preserve">SIF_hbm_stk_28</t>
     </r>
   </si>
   <si>
@@ -7786,26 +7596,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7824,7 +7615,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D47:F47</t>
+      <t xml:space="preserve">SIF_hbm_stk_29</t>
     </r>
   </si>
   <si>
@@ -7870,26 +7661,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7908,7 +7680,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D48:F48</t>
+      <t xml:space="preserve">SIF_hbm_stk_30</t>
     </r>
   </si>
   <si>
@@ -8249,26 +8021,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8287,7 +8040,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D66:F66</t>
+      <t xml:space="preserve">SIF_hbm_hbp_25</t>
     </r>
   </si>
   <si>
@@ -8676,26 +8429,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8714,7 +8448,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D67:F67</t>
+      <t xml:space="preserve">SIF_hbm_hbp_26</t>
     </r>
   </si>
   <si>
@@ -8797,26 +8531,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8835,7 +8550,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D68:F68</t>
+      <t xml:space="preserve">SIF_hbm_hbp_27</t>
     </r>
   </si>
   <si>
@@ -8918,26 +8633,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8956,7 +8652,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D69:F69</t>
+      <t xml:space="preserve">SIF_hbm_hbp_28</t>
     </r>
   </si>
   <si>
@@ -9039,26 +8735,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -9077,7 +8754,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D70:F70</t>
+      <t xml:space="preserve">SIF_hbm_hbp_29</t>
     </r>
   </si>
   <si>
@@ -9160,26 +8837,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -9198,7 +8856,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D71:F71</t>
+      <t xml:space="preserve">SIF_hbm_hbp_30</t>
     </r>
   </si>
   <si>

--- a/hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx
+++ b/hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx
@@ -33365,7 +33365,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；混合鍵合高值；份額回落、毛利率下調</t>
+      <t xml:space="preserve">；混合鍵合低值（導入慢）；份額回落、毛利率下調</t>
     </r>
   </si>
   <si>

--- a/hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx
+++ b/hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx
@@ -9795,26 +9795,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">samsung/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9888,26 +9888,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">samsung/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9981,26 +9981,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">samsung/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10074,26 +10074,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">samsung/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10167,26 +10167,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">samsung/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10260,26 +10260,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">micron/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10353,26 +10353,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">micron/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10446,26 +10446,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">micron/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10539,26 +10539,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">micron/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10632,26 +10632,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">micron/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
